--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/27.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/27.xlsx
@@ -426,13 +426,13 @@
         <v>-8.802797073006372</v>
       </c>
       <c r="E2">
-        <v>-6.925546816280133</v>
+        <v>-4.612569846700398</v>
       </c>
       <c r="F2">
-        <v>-6.261414383667944</v>
+        <v>-6.931034699946057</v>
       </c>
       <c r="G2">
-        <v>-5.767951401558366</v>
+        <v>-6.74563495239809</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.05356678640414</v>
       </c>
       <c r="E3">
-        <v>-6.504444018306867</v>
+        <v>-4.685202041309423</v>
       </c>
       <c r="F3">
-        <v>-6.438806363691548</v>
+        <v>-6.600950999115524</v>
       </c>
       <c r="G3">
-        <v>-5.323679500733712</v>
+        <v>-6.334743282245907</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.75536981672811</v>
       </c>
       <c r="E4">
-        <v>-7.378204021138846</v>
+        <v>-5.567412176639716</v>
       </c>
       <c r="F4">
-        <v>-6.537607400558251</v>
+        <v>-6.682308275214075</v>
       </c>
       <c r="G4">
-        <v>-5.939242338305797</v>
+        <v>-6.738199467116887</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.64744146185652</v>
       </c>
       <c r="E5">
-        <v>-8.573639646631683</v>
+        <v>-6.552518298372295</v>
       </c>
       <c r="F5">
-        <v>-6.050550561999421</v>
+        <v>-6.23708440468032</v>
       </c>
       <c r="G5">
-        <v>-5.934018297444827</v>
+        <v>-6.790072405171728</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.65376578351442</v>
       </c>
       <c r="E6">
-        <v>-7.778018462802055</v>
+        <v>-7.43730966388696</v>
       </c>
       <c r="F6">
-        <v>-6.114696848570006</v>
+        <v>-6.508610399623254</v>
       </c>
       <c r="G6">
-        <v>-6.609985348926453</v>
+        <v>-7.614351896812703</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.61079911690457</v>
       </c>
       <c r="E7">
-        <v>-9.687173291221793</v>
+        <v>-7.642019331403699</v>
       </c>
       <c r="F7">
-        <v>-6.512326455792213</v>
+        <v>-6.37593741965608</v>
       </c>
       <c r="G7">
-        <v>-5.859269489713623</v>
+        <v>-7.145942808461223</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.39469790430793</v>
       </c>
       <c r="E8">
-        <v>-10.27638662978181</v>
+        <v>-8.373204858578186</v>
       </c>
       <c r="F8">
-        <v>-6.347403476099248</v>
+        <v>-6.459674595302873</v>
       </c>
       <c r="G8">
-        <v>-6.880648931126187</v>
+        <v>-7.025640894109647</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.86400803103077</v>
       </c>
       <c r="E9">
-        <v>-11.00199760545285</v>
+        <v>-10.18862480351315</v>
       </c>
       <c r="F9">
-        <v>-6.223674378980101</v>
+        <v>-6.157235171438566</v>
       </c>
       <c r="G9">
-        <v>-5.56134687554353</v>
+        <v>-7.029765833851579</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.91250867707884</v>
       </c>
       <c r="E10">
-        <v>-11.41775227562306</v>
+        <v>-9.460025034997047</v>
       </c>
       <c r="F10">
-        <v>-6.266877466689407</v>
+        <v>-6.172087798970761</v>
       </c>
       <c r="G10">
-        <v>-6.262507178579011</v>
+        <v>-6.505378730976562</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-22.45223729694878</v>
       </c>
       <c r="E11">
-        <v>-12.55388300551144</v>
+        <v>-10.83285457279236</v>
       </c>
       <c r="F11">
-        <v>-5.62570660049304</v>
+        <v>-5.920591313643817</v>
       </c>
       <c r="G11">
-        <v>-5.81172012413307</v>
+        <v>-7.026147407577156</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-22.43420393498453</v>
       </c>
       <c r="E12">
-        <v>-12.01124955059433</v>
+        <v>-10.53919661881696</v>
       </c>
       <c r="F12">
-        <v>-5.622395615984051</v>
+        <v>-5.978369939989083</v>
       </c>
       <c r="G12">
-        <v>-5.203903963122881</v>
+        <v>-6.140639376187359</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-21.84241648907371</v>
       </c>
       <c r="E13">
-        <v>-12.06460855982671</v>
+        <v>-11.35934401787213</v>
       </c>
       <c r="F13">
-        <v>-5.941623562000896</v>
+        <v>-5.683919291357373</v>
       </c>
       <c r="G13">
-        <v>-5.091130229327607</v>
+        <v>-5.7608900079231</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-20.70868908119784</v>
       </c>
       <c r="E14">
-        <v>-14.21383138081507</v>
+        <v>-12.09503537668424</v>
       </c>
       <c r="F14">
-        <v>-5.179207458342677</v>
+        <v>-5.604755532141436</v>
       </c>
       <c r="G14">
-        <v>-5.668668140835623</v>
+        <v>-5.751574132775591</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.10460280059488</v>
       </c>
       <c r="E15">
-        <v>-13.87427281429793</v>
+        <v>-12.25796987148022</v>
       </c>
       <c r="F15">
-        <v>-5.091230698328355</v>
+        <v>-5.487154697068198</v>
       </c>
       <c r="G15">
-        <v>-4.52182564457576</v>
+        <v>-5.330088716897741</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.14173352532621</v>
       </c>
       <c r="E16">
-        <v>-14.84359720411378</v>
+        <v>-13.5207937186812</v>
       </c>
       <c r="F16">
-        <v>-5.321443939975171</v>
+        <v>-5.390518184225011</v>
       </c>
       <c r="G16">
-        <v>-3.90601120554269</v>
+        <v>-4.871101441151026</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.96222373817791</v>
       </c>
       <c r="E17">
-        <v>-15.60520501967179</v>
+        <v>-13.43717997460358</v>
       </c>
       <c r="F17">
-        <v>-4.805973271132914</v>
+        <v>-5.301554010266552</v>
       </c>
       <c r="G17">
-        <v>-2.702204152188587</v>
+        <v>-3.962469249169421</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.72135768315761</v>
       </c>
       <c r="E18">
-        <v>-15.02812799145233</v>
+        <v>-15.05976843934393</v>
       </c>
       <c r="F18">
-        <v>-4.258229408277589</v>
+        <v>-4.858867843271274</v>
       </c>
       <c r="G18">
-        <v>-3.171473982380278</v>
+        <v>-3.508398133548524</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.57040516579586</v>
       </c>
       <c r="E19">
-        <v>-17.65547615511855</v>
+        <v>-14.81503159007339</v>
       </c>
       <c r="F19">
-        <v>-4.3096006127622</v>
+        <v>-4.542090208031909</v>
       </c>
       <c r="G19">
-        <v>-2.270383213137132</v>
+        <v>-3.529486308633682</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.642721165450213</v>
       </c>
       <c r="E20">
-        <v>-18.25128748030774</v>
+        <v>-15.12235195012993</v>
       </c>
       <c r="F20">
-        <v>-4.045206446973668</v>
+        <v>-4.588332989925789</v>
       </c>
       <c r="G20">
-        <v>-2.133611334727682</v>
+        <v>-3.645895021431075</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.033142619021524</v>
       </c>
       <c r="E21">
-        <v>-18.49901765089735</v>
+        <v>-15.80985128855242</v>
       </c>
       <c r="F21">
-        <v>-3.630589509422251</v>
+        <v>-4.169570901890763</v>
       </c>
       <c r="G21">
-        <v>-2.693139878502063</v>
+        <v>-2.961446352277835</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.798883260124054</v>
       </c>
       <c r="E22">
-        <v>-19.33739215783339</v>
+        <v>-15.65165810604247</v>
       </c>
       <c r="F22">
-        <v>-3.540191431489546</v>
+        <v>-4.072733095768696</v>
       </c>
       <c r="G22">
-        <v>-2.949548251609694</v>
+        <v>-3.533041834542859</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.956925817893968</v>
       </c>
       <c r="E23">
-        <v>-19.12760607095406</v>
+        <v>-16.3413039411446</v>
       </c>
       <c r="F23">
-        <v>-3.419965500116838</v>
+        <v>-4.132699440424754</v>
       </c>
       <c r="G23">
-        <v>-3.029812428209324</v>
+        <v>-3.258902179526891</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.486543549883049</v>
       </c>
       <c r="E24">
-        <v>-19.77558994518562</v>
+        <v>-17.37798938182454</v>
       </c>
       <c r="F24">
-        <v>-3.201242542714253</v>
+        <v>-3.509256050831999</v>
       </c>
       <c r="G24">
-        <v>-3.461454597801659</v>
+        <v>-2.693818540337613</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.346158328086383</v>
       </c>
       <c r="E25">
-        <v>-19.84316836280208</v>
+        <v>-17.57118766841378</v>
       </c>
       <c r="F25">
-        <v>-3.256898063406144</v>
+        <v>-3.434801560300976</v>
       </c>
       <c r="G25">
-        <v>-3.234599464723101</v>
+        <v>-3.457869276982628</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.474589591665227</v>
       </c>
       <c r="E26">
-        <v>-21.41660477066318</v>
+        <v>-17.53520894242284</v>
       </c>
       <c r="F26">
-        <v>-2.689370301869757</v>
+        <v>-3.637557736014601</v>
       </c>
       <c r="G26">
-        <v>-3.687998539599525</v>
+        <v>-3.218933963231269</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.80194457107513</v>
       </c>
       <c r="E27">
-        <v>-19.32743404349053</v>
+        <v>-17.86828273416101</v>
       </c>
       <c r="F27">
-        <v>-3.038209069067074</v>
+        <v>-3.666124814267544</v>
       </c>
       <c r="G27">
-        <v>-4.225187522074904</v>
+        <v>-3.553464589974623</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.261645908439943</v>
       </c>
       <c r="E28">
-        <v>-20.34756791167244</v>
+        <v>-18.063106742919</v>
       </c>
       <c r="F28">
-        <v>-2.985434610202121</v>
+        <v>-3.509568345342855</v>
       </c>
       <c r="G28">
-        <v>-4.384775680341011</v>
+        <v>-3.879414282680185</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.794288682514558</v>
       </c>
       <c r="E29">
-        <v>-20.55884839497431</v>
+        <v>-17.26739498960922</v>
       </c>
       <c r="F29">
-        <v>-3.047812332367729</v>
+        <v>-3.480429693581979</v>
       </c>
       <c r="G29">
-        <v>-3.751468318678433</v>
+        <v>-3.455071866001944</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.350995043257158</v>
       </c>
       <c r="E30">
-        <v>-20.506716602198</v>
+        <v>-17.06931953651372</v>
       </c>
       <c r="F30">
-        <v>-2.875947633839304</v>
+        <v>-3.598056208044703</v>
       </c>
       <c r="G30">
-        <v>-3.871462352294856</v>
+        <v>-3.993515545236706</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.897559002726064</v>
       </c>
       <c r="E31">
-        <v>-19.70672544095097</v>
+        <v>-17.98560191027772</v>
       </c>
       <c r="F31">
-        <v>-3.108126591332963</v>
+        <v>-3.864499754787762</v>
       </c>
       <c r="G31">
-        <v>-4.349488575437919</v>
+        <v>-3.840700763143948</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.408091722566536</v>
       </c>
       <c r="E32">
-        <v>-19.99886182765979</v>
+        <v>-17.48224843890314</v>
       </c>
       <c r="F32">
-        <v>-3.578326981612227</v>
+        <v>-3.942353865139873</v>
       </c>
       <c r="G32">
-        <v>-3.776380173861448</v>
+        <v>-3.474369035950356</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.870304527811995</v>
       </c>
       <c r="E33">
-        <v>-19.42384072663982</v>
+        <v>-17.29301709554462</v>
       </c>
       <c r="F33">
-        <v>-3.48178821612257</v>
+        <v>-3.921177480854706</v>
       </c>
       <c r="G33">
-        <v>-2.63205369221143</v>
+        <v>-3.62111558806963</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.280007491693009</v>
       </c>
       <c r="E34">
-        <v>-19.30312519501735</v>
+        <v>-16.69009153768938</v>
       </c>
       <c r="F34">
-        <v>-3.523579351593805</v>
+        <v>-3.986776723849802</v>
       </c>
       <c r="G34">
-        <v>-3.194230672417228</v>
+        <v>-2.751753087274859</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.637619997866073</v>
       </c>
       <c r="E35">
-        <v>-18.65088002674457</v>
+        <v>-16.31983444587424</v>
       </c>
       <c r="F35">
-        <v>-3.502291137709261</v>
+        <v>-3.646755099287883</v>
       </c>
       <c r="G35">
-        <v>-3.306137043281212</v>
+        <v>-3.232778664676502</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.946730446448592</v>
       </c>
       <c r="E36">
-        <v>-18.47169283873507</v>
+        <v>-16.40670416276338</v>
       </c>
       <c r="F36">
-        <v>-3.163352189342801</v>
+        <v>-4.153341527735115</v>
       </c>
       <c r="G36">
-        <v>-2.612124208065018</v>
+        <v>-2.634811376645643</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.210562394566338</v>
       </c>
       <c r="E37">
-        <v>-18.33886816761609</v>
+        <v>-15.98964529207896</v>
       </c>
       <c r="F37">
-        <v>-3.494516909633987</v>
+        <v>-4.010682578727192</v>
       </c>
       <c r="G37">
-        <v>-3.216361669347256</v>
+        <v>-2.541414265891725</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.428841022418084</v>
       </c>
       <c r="E38">
-        <v>-18.48815384175295</v>
+        <v>-15.10451429101372</v>
       </c>
       <c r="F38">
-        <v>-3.454983075335381</v>
+        <v>-4.194713509300533</v>
       </c>
       <c r="G38">
-        <v>-2.483502892773254</v>
+        <v>-2.786447604526421</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.600922287101804</v>
       </c>
       <c r="E39">
-        <v>-18.48345781420699</v>
+        <v>-14.40277743031111</v>
       </c>
       <c r="F39">
-        <v>-3.514758895488796</v>
+        <v>-3.860722399430995</v>
       </c>
       <c r="G39">
-        <v>-2.989460188631148</v>
+        <v>-2.529526096860202</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.720655293856177</v>
       </c>
       <c r="E40">
-        <v>-18.23774734302481</v>
+        <v>-14.86129448053575</v>
       </c>
       <c r="F40">
-        <v>-3.313717440298967</v>
+        <v>-4.07641850234375</v>
       </c>
       <c r="G40">
-        <v>-1.299929893755176</v>
+        <v>-2.500383364477997</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.777155392550348</v>
       </c>
       <c r="E41">
-        <v>-18.32242075002023</v>
+        <v>-15.16292254876465</v>
       </c>
       <c r="F41">
-        <v>-3.643099513939329</v>
+        <v>-3.728623478073961</v>
       </c>
       <c r="G41">
-        <v>-1.128979943198291</v>
+        <v>-2.149458916224173</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.761006519425788</v>
       </c>
       <c r="E42">
-        <v>-16.94729074742903</v>
+        <v>-13.09715044678963</v>
       </c>
       <c r="F42">
-        <v>-3.282035700611497</v>
+        <v>-4.106077368833584</v>
       </c>
       <c r="G42">
-        <v>-1.826594651961211</v>
+        <v>-2.354262505465646</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.663820899084907</v>
       </c>
       <c r="E43">
-        <v>-17.04989238302081</v>
+        <v>-14.18418798996086</v>
       </c>
       <c r="F43">
-        <v>-3.127706711632936</v>
+        <v>-4.19715636477139</v>
       </c>
       <c r="G43">
-        <v>-1.676332300479231</v>
+        <v>-2.447113376205585</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.482508726235205</v>
       </c>
       <c r="E44">
-        <v>-16.80586650416948</v>
+        <v>-13.05020375675211</v>
       </c>
       <c r="F44">
-        <v>-3.633495422271272</v>
+        <v>-4.24353251381712</v>
       </c>
       <c r="G44">
-        <v>-1.261285895675264</v>
+        <v>-1.765875936225439</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.220631446804079</v>
       </c>
       <c r="E45">
-        <v>-16.18066538267051</v>
+        <v>-13.26991625865626</v>
       </c>
       <c r="F45">
-        <v>-3.351585427750544</v>
+        <v>-4.228090088694132</v>
       </c>
       <c r="G45">
-        <v>-2.26902920001157</v>
+        <v>-1.916558726990906</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.888103093035982</v>
       </c>
       <c r="E46">
-        <v>-15.2739426175367</v>
+        <v>-12.92132338649382</v>
       </c>
       <c r="F46">
-        <v>-3.818021716551486</v>
+        <v>-4.536127619466559</v>
       </c>
       <c r="G46">
-        <v>-1.547326961904912</v>
+        <v>-1.433970572094727</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.501828390967205</v>
       </c>
       <c r="E47">
-        <v>-16.29837400755189</v>
+        <v>-12.75548161138491</v>
       </c>
       <c r="F47">
-        <v>-3.653375411571057</v>
+        <v>-4.373187751335895</v>
       </c>
       <c r="G47">
-        <v>-1.560413548421651</v>
+        <v>-2.374407175072111</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.086731859286195</v>
       </c>
       <c r="E48">
-        <v>-15.20512792651614</v>
+        <v>-12.70858926303549</v>
       </c>
       <c r="F48">
-        <v>-3.597949348649742</v>
+        <v>-4.387996475395743</v>
       </c>
       <c r="G48">
-        <v>-1.626432447565797</v>
+        <v>-2.428385620089928</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.668902010711784</v>
       </c>
       <c r="E49">
-        <v>-13.9303443794609</v>
+        <v>-11.26549139406316</v>
       </c>
       <c r="F49">
-        <v>-3.683925601386303</v>
+        <v>-4.691334677892088</v>
       </c>
       <c r="G49">
-        <v>-1.895636079182712</v>
+        <v>-1.822486264946976</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.277528989945723</v>
       </c>
       <c r="E50">
-        <v>-12.98464956701708</v>
+        <v>-12.25307459107793</v>
       </c>
       <c r="F50">
-        <v>-4.033410495157803</v>
+        <v>-4.553369258588427</v>
       </c>
       <c r="G50">
-        <v>-1.784736114162667</v>
+        <v>-2.27488555507054</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.939606271907659</v>
       </c>
       <c r="E51">
-        <v>-14.69866792197229</v>
+        <v>-10.80863629379933</v>
       </c>
       <c r="F51">
-        <v>-3.739292021854616</v>
+        <v>-5.035724283768968</v>
       </c>
       <c r="G51">
-        <v>-1.842723629828541</v>
+        <v>-1.914274450568809</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.677770624616674</v>
       </c>
       <c r="E52">
-        <v>-14.61702859256201</v>
+        <v>-11.29411134979163</v>
       </c>
       <c r="F52">
-        <v>-4.117483987970133</v>
+        <v>-4.819599914908967</v>
       </c>
       <c r="G52">
-        <v>-1.985166472746762</v>
+        <v>-1.826088138493703</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.512530505586111</v>
       </c>
       <c r="E53">
-        <v>-13.65800195263961</v>
+        <v>-10.78156507618148</v>
       </c>
       <c r="F53">
-        <v>-4.434621134662312</v>
+        <v>-4.896794644808449</v>
       </c>
       <c r="G53">
-        <v>-1.960973005945768</v>
+        <v>-1.535365960871525</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.457739195768483</v>
       </c>
       <c r="E54">
-        <v>-13.44472894077436</v>
+        <v>-10.03268680105903</v>
       </c>
       <c r="F54">
-        <v>-4.055179162135971</v>
+        <v>-4.765229192058817</v>
       </c>
       <c r="G54">
-        <v>-2.49074305586764</v>
+        <v>-2.156368024764632</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.518984696322116</v>
       </c>
       <c r="E55">
-        <v>-14.00297204559592</v>
+        <v>-9.099499633824388</v>
       </c>
       <c r="F55">
-        <v>-4.135570561842858</v>
+        <v>-4.94065587041928</v>
       </c>
       <c r="G55">
-        <v>-2.401583443403988</v>
+        <v>-2.364886046101167</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.695714335178773</v>
       </c>
       <c r="E56">
-        <v>-11.99444891202587</v>
+        <v>-9.49248513668403</v>
       </c>
       <c r="F56">
-        <v>-4.107523698318872</v>
+        <v>-5.089498582089101</v>
       </c>
       <c r="G56">
-        <v>-1.907957929679879</v>
+        <v>-2.415252685935639</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.977237072153299</v>
       </c>
       <c r="E57">
-        <v>-14.371417747808</v>
+        <v>-8.476422366635015</v>
       </c>
       <c r="F57">
-        <v>-4.632942231301348</v>
+        <v>-5.308898315659772</v>
       </c>
       <c r="G57">
-        <v>-2.826164219361057</v>
+        <v>-2.073435548460349</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.34308074047324</v>
       </c>
       <c r="E58">
-        <v>-12.90685944051332</v>
+        <v>-9.254051923232169</v>
       </c>
       <c r="F58">
-        <v>-4.16804587750221</v>
+        <v>-5.15165761526037</v>
       </c>
       <c r="G58">
-        <v>-2.33421384167982</v>
+        <v>-2.549588002828185</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.76782512311468</v>
       </c>
       <c r="E59">
-        <v>-11.92271788374437</v>
+        <v>-9.698018986470164</v>
       </c>
       <c r="F59">
-        <v>-4.388795849939444</v>
+        <v>-5.104608003516164</v>
       </c>
       <c r="G59">
-        <v>-3.35738428822913</v>
+        <v>-2.008707762076519</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.218208562181477</v>
       </c>
       <c r="E60">
-        <v>-12.11194017015488</v>
+        <v>-9.163070351944064</v>
       </c>
       <c r="F60">
-        <v>-4.225717644452514</v>
+        <v>-5.360320050555955</v>
       </c>
       <c r="G60">
-        <v>-1.528913707615486</v>
+        <v>-2.393922841026115</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.662387640377371</v>
       </c>
       <c r="E61">
-        <v>-11.68717383670941</v>
+        <v>-8.500409693453646</v>
       </c>
       <c r="F61">
-        <v>-4.73265447231113</v>
+        <v>-5.444620516036652</v>
       </c>
       <c r="G61">
-        <v>-2.57604919332358</v>
+        <v>-2.450304742105442</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.07137435723185</v>
       </c>
       <c r="E62">
-        <v>-11.58372537647818</v>
+        <v>-9.271033700760933</v>
       </c>
       <c r="F62">
-        <v>-4.433309829063681</v>
+        <v>-5.213001534907285</v>
       </c>
       <c r="G62">
-        <v>-2.505226692601951</v>
+        <v>-2.578283811562588</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.421591644364003</v>
       </c>
       <c r="E63">
-        <v>-11.38787340412045</v>
+        <v>-8.10556751625086</v>
       </c>
       <c r="F63">
-        <v>-4.517411486367706</v>
+        <v>-5.153327603944414</v>
       </c>
       <c r="G63">
-        <v>-3.083079105936198</v>
+        <v>-2.256892740064602</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.698533028766001</v>
       </c>
       <c r="E64">
-        <v>-11.47564428733712</v>
+        <v>-7.65323183304669</v>
       </c>
       <c r="F64">
-        <v>-4.559355041441057</v>
+        <v>-5.451339404040759</v>
       </c>
       <c r="G64">
-        <v>-2.455204349503564</v>
+        <v>-2.752034483645697</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.894111463640577</v>
       </c>
       <c r="E65">
-        <v>-10.74785511566838</v>
+        <v>-9.120919315880668</v>
       </c>
       <c r="F65">
-        <v>-4.503757506467363</v>
+        <v>-5.582308432260374</v>
       </c>
       <c r="G65">
-        <v>-2.742748403408041</v>
+        <v>-2.647179574780361</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.00218423257675</v>
       </c>
       <c r="E66">
-        <v>-11.62530582481661</v>
+        <v>-8.537362041356236</v>
       </c>
       <c r="F66">
-        <v>-4.742714166050727</v>
+        <v>-5.022372657970646</v>
       </c>
       <c r="G66">
-        <v>-3.257101242753527</v>
+        <v>-2.449324820625818</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.02589577540512</v>
       </c>
       <c r="E67">
-        <v>-10.8877894909794</v>
+        <v>-8.084944845619928</v>
       </c>
       <c r="F67">
-        <v>-4.27722635792599</v>
+        <v>-5.331030635927769</v>
       </c>
       <c r="G67">
-        <v>-2.880731941484864</v>
+        <v>-2.060252956122972</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.973978808920434</v>
       </c>
       <c r="E68">
-        <v>-11.03404108753113</v>
+        <v>-8.156540019681197</v>
       </c>
       <c r="F68">
-        <v>-4.470219395430219</v>
+        <v>-5.427103858937054</v>
       </c>
       <c r="G68">
-        <v>-2.608224385419756</v>
+        <v>-2.296195536706829</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.856671837304098</v>
       </c>
       <c r="E69">
-        <v>-11.96368698809177</v>
+        <v>-7.789874007754135</v>
       </c>
       <c r="F69">
-        <v>-4.867733859583437</v>
+        <v>-5.576581928404821</v>
       </c>
       <c r="G69">
-        <v>-2.760310847493875</v>
+        <v>-2.263656184601333</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.685265395459782</v>
       </c>
       <c r="E70">
-        <v>-11.53424726947038</v>
+        <v>-7.875475751921129</v>
       </c>
       <c r="F70">
-        <v>-4.564050227880124</v>
+        <v>-5.377215432103453</v>
       </c>
       <c r="G70">
-        <v>-2.320097675500367</v>
+        <v>-2.079073407513728</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.467744395687303</v>
       </c>
       <c r="E71">
-        <v>-11.09043870282265</v>
+        <v>-9.029919630696533</v>
       </c>
       <c r="F71">
-        <v>-4.443247752795067</v>
+        <v>-5.817065269111546</v>
       </c>
       <c r="G71">
-        <v>-2.509828350901538</v>
+        <v>-2.080192371906002</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.211934822216231</v>
       </c>
       <c r="E72">
-        <v>-11.09683290812148</v>
+        <v>-8.053435723474559</v>
       </c>
       <c r="F72">
-        <v>-4.33340540681645</v>
+        <v>-5.9618638911209</v>
       </c>
       <c r="G72">
-        <v>-2.965554739292071</v>
+        <v>-2.072445695344108</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.927756511786534</v>
       </c>
       <c r="E73">
-        <v>-11.59924898537648</v>
+        <v>-8.321299489502268</v>
       </c>
       <c r="F73">
-        <v>-4.674833599228322</v>
+        <v>-5.80066193780131</v>
       </c>
       <c r="G73">
-        <v>-2.59367453777466</v>
+        <v>-1.858839365513713</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.625175897465823</v>
       </c>
       <c r="E74">
-        <v>-12.82258906770458</v>
+        <v>-8.394579255894389</v>
       </c>
       <c r="F74">
-        <v>-5.065088251463405</v>
+        <v>-5.83733541945805</v>
       </c>
       <c r="G74">
-        <v>-2.520984889368882</v>
+        <v>-1.589725118626358</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.314203508363939</v>
       </c>
       <c r="E75">
-        <v>-11.01046132337319</v>
+        <v>-8.994959811357317</v>
       </c>
       <c r="F75">
-        <v>-4.575968778071603</v>
+        <v>-5.891499050457498</v>
       </c>
       <c r="G75">
-        <v>-2.000090412037796</v>
+        <v>-1.352296103095368</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.007796728012467</v>
       </c>
       <c r="E76">
-        <v>-11.83512813948801</v>
+        <v>-9.672247440892511</v>
       </c>
       <c r="F76">
-        <v>-5.019158592447784</v>
+        <v>-5.980858355667093</v>
       </c>
       <c r="G76">
-        <v>-2.17550297798162</v>
+        <v>-1.057581407552829</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.716814429379147</v>
       </c>
       <c r="E77">
-        <v>-12.32522676744214</v>
+        <v>-9.936257475539692</v>
       </c>
       <c r="F77">
-        <v>-4.888915214073021</v>
+        <v>-6.224121697377612</v>
       </c>
       <c r="G77">
-        <v>-1.881152442448401</v>
+        <v>-1.032556993821478</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.453921120920322</v>
       </c>
       <c r="E78">
-        <v>-12.43721140117782</v>
+        <v>-9.990413496197423</v>
       </c>
       <c r="F78">
-        <v>-5.191146717719225</v>
+        <v>-6.007108490294406</v>
       </c>
       <c r="G78">
-        <v>-2.839194526603629</v>
+        <v>-1.788688905536556</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.229919944839242</v>
       </c>
       <c r="E79">
-        <v>-12.97805610886191</v>
+        <v>-10.77711811470595</v>
       </c>
       <c r="F79">
-        <v>-5.607136260057081</v>
+        <v>-6.489622562016284</v>
       </c>
       <c r="G79">
-        <v>-1.568064219162907</v>
+        <v>-1.383958160632957</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.051777805539887</v>
       </c>
       <c r="E80">
-        <v>-13.7274279876512</v>
+        <v>-11.28871340877449</v>
       </c>
       <c r="F80">
-        <v>-5.290500275643596</v>
+        <v>-6.429850883699883</v>
       </c>
       <c r="G80">
-        <v>-1.914218171294641</v>
+        <v>-1.529052750528135</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.924595060482826</v>
       </c>
       <c r="E81">
-        <v>-14.29146301072857</v>
+        <v>-12.09847701693007</v>
       </c>
       <c r="F81">
-        <v>-4.810528463480908</v>
+        <v>-6.152130771502515</v>
       </c>
       <c r="G81">
-        <v>-2.181571207955104</v>
+        <v>-1.289773140040692</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.84912189427453</v>
       </c>
       <c r="E82">
-        <v>-16.00833430430862</v>
+        <v>-12.6731177261334</v>
       </c>
       <c r="F82">
-        <v>-5.081509806856503</v>
+        <v>-6.556181468647523</v>
       </c>
       <c r="G82">
-        <v>-2.234304887850155</v>
+        <v>-1.191158609516882</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.820521432692527</v>
       </c>
       <c r="E83">
-        <v>-14.98219115111853</v>
+        <v>-13.37156238623243</v>
       </c>
       <c r="F83">
-        <v>-5.517726424435916</v>
+        <v>-6.622988885499602</v>
       </c>
       <c r="G83">
-        <v>-2.186510541899696</v>
+        <v>-0.6609813624936799</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.83049072110078</v>
       </c>
       <c r="E84">
-        <v>-15.75512920864373</v>
+        <v>-14.08707033639237</v>
       </c>
       <c r="F84">
-        <v>-5.971187994606811</v>
+        <v>-6.649207542165609</v>
       </c>
       <c r="G84">
-        <v>-2.741066646274092</v>
+        <v>-0.6227776669704903</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.864886508801956</v>
       </c>
       <c r="E85">
-        <v>-18.15879339870108</v>
+        <v>-15.99387035832811</v>
       </c>
       <c r="F85">
-        <v>-5.423632999519324</v>
+        <v>-6.815122077639725</v>
       </c>
       <c r="G85">
-        <v>-2.174963359058718</v>
+        <v>-0.7809853277467211</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.906027239500382</v>
       </c>
       <c r="E86">
-        <v>-18.42216944698718</v>
+        <v>-16.43047865130364</v>
       </c>
       <c r="F86">
-        <v>-5.633245572225919</v>
+        <v>-6.599203558079318</v>
       </c>
       <c r="G86">
-        <v>-1.970749046923236</v>
+        <v>-1.061272665829116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.941190940707068</v>
       </c>
       <c r="E87">
-        <v>-19.71856740048103</v>
+        <v>-18.05446188603836</v>
       </c>
       <c r="F87">
-        <v>-5.644122036224676</v>
+        <v>-6.634638216285171</v>
       </c>
       <c r="G87">
-        <v>-2.182713346166152</v>
+        <v>-0.7278179663860258</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.958137168824389</v>
       </c>
       <c r="E88">
-        <v>-21.13839797000195</v>
+        <v>-18.28061387798142</v>
       </c>
       <c r="F88">
-        <v>-5.463526345270745</v>
+        <v>-6.934481950892807</v>
       </c>
       <c r="G88">
-        <v>-1.238244498721936</v>
+        <v>-0.3720005318251587</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.949053311311979</v>
       </c>
       <c r="E89">
-        <v>-23.46976507252683</v>
+        <v>-20.4185698556387</v>
       </c>
       <c r="F89">
-        <v>-6.160392079610634</v>
+        <v>-6.821482282558419</v>
       </c>
       <c r="G89">
-        <v>-1.912930369079865</v>
+        <v>-1.007678244093855</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.911407590072332</v>
       </c>
       <c r="E90">
-        <v>-24.02391896531946</v>
+        <v>-21.92549203727513</v>
       </c>
       <c r="F90">
-        <v>-6.086105747662381</v>
+        <v>-7.118948188536319</v>
       </c>
       <c r="G90">
-        <v>-2.032500652867261</v>
+        <v>-1.145310864343515</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.84762527962986</v>
       </c>
       <c r="E91">
-        <v>-26.11636830767366</v>
+        <v>-23.63876772249309</v>
       </c>
       <c r="F91">
-        <v>-5.78446735507658</v>
+        <v>-6.710193607094515</v>
       </c>
       <c r="G91">
-        <v>-1.983137108331189</v>
+        <v>-1.403609558954071</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.766880215370238</v>
       </c>
       <c r="E92">
-        <v>-27.56211533394048</v>
+        <v>-26.47859641507321</v>
       </c>
       <c r="F92">
-        <v>-6.250731343457741</v>
+        <v>-7.111434067825525</v>
       </c>
       <c r="G92">
-        <v>-3.026574714671917</v>
+        <v>-1.876050891772384</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.685624301812251</v>
       </c>
       <c r="E93">
-        <v>-30.08977819927585</v>
+        <v>-28.44188009330663</v>
       </c>
       <c r="F93">
-        <v>-6.201795539137359</v>
+        <v>-6.78270806116818</v>
       </c>
       <c r="G93">
-        <v>-2.602344856542011</v>
+        <v>-1.821618902015687</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.623706476707985</v>
       </c>
       <c r="E94">
-        <v>-30.64897454787602</v>
+        <v>-30.15549088560116</v>
       </c>
       <c r="F94">
-        <v>-5.643171898813665</v>
+        <v>-6.649748466079637</v>
       </c>
       <c r="G94">
-        <v>-2.780346269097544</v>
+        <v>-2.503607835833248</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.60473668742411</v>
       </c>
       <c r="E95">
-        <v>-33.4181703671215</v>
+        <v>-32.49122796554344</v>
       </c>
       <c r="F95">
-        <v>-5.349567013300215</v>
+        <v>-6.739815197051222</v>
       </c>
       <c r="G95">
-        <v>-4.434523248159639</v>
+        <v>-2.615845261251159</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.654153341483878</v>
       </c>
       <c r="E96">
-        <v>-36.72109666138502</v>
+        <v>-33.7301324130359</v>
       </c>
       <c r="F96">
-        <v>-6.01542447065111</v>
+        <v>-6.77646755533919</v>
       </c>
       <c r="G96">
-        <v>-3.767282794719531</v>
+        <v>-3.03069634386831</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.780435458030914</v>
       </c>
       <c r="E97">
-        <v>-37.63647107611049</v>
+        <v>-35.52369114969885</v>
       </c>
       <c r="F97">
-        <v>-5.681826835297901</v>
+        <v>-6.629996873727285</v>
       </c>
       <c r="G97">
-        <v>-3.935259875382151</v>
+        <v>-3.699307363161676</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.004559887440318</v>
       </c>
       <c r="E98">
-        <v>-41.23150885047578</v>
+        <v>-38.7888567634494</v>
       </c>
       <c r="F98">
-        <v>-5.725306183536042</v>
+        <v>-6.610907146929771</v>
       </c>
       <c r="G98">
-        <v>-4.738623340306011</v>
+        <v>-4.028988040689997</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.306327169327294</v>
       </c>
       <c r="E99">
-        <v>-44.22747932684038</v>
+        <v>-41.5920659509665</v>
       </c>
       <c r="F99">
-        <v>-6.053573274652235</v>
+        <v>-6.634736792006104</v>
       </c>
       <c r="G99">
-        <v>-4.323083664216692</v>
+        <v>-4.483727886509826</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.702022579605337</v>
       </c>
       <c r="E100">
-        <v>-45.87285733702433</v>
+        <v>-44.03163414719366</v>
       </c>
       <c r="F100">
-        <v>-5.753879060360806</v>
+        <v>-6.403684828363954</v>
       </c>
       <c r="G100">
-        <v>-5.409022054190584</v>
+        <v>-5.345065624917404</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.12831338613465</v>
       </c>
       <c r="E101">
-        <v>-48.07559087112433</v>
+        <v>-46.34472206438658</v>
       </c>
       <c r="F101">
-        <v>-5.434220363294505</v>
+        <v>-6.137646767464566</v>
       </c>
       <c r="G101">
-        <v>-5.387957052924201</v>
+        <v>-5.008926073041964</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.642019160626965</v>
       </c>
       <c r="E102">
-        <v>-49.9074231379816</v>
+        <v>-48.57282184564055</v>
       </c>
       <c r="F102">
-        <v>-5.446762674140292</v>
+        <v>-6.004141278257578</v>
       </c>
       <c r="G102">
-        <v>-5.754702598310203</v>
+        <v>-5.977641356015803</v>
       </c>
     </row>
   </sheetData>
